--- a/artfynd/A 57076-2024 artfynd.xlsx
+++ b/artfynd/A 57076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80685764</v>
+        <v>80685751</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545718.8449529386</v>
+        <v>545730</v>
       </c>
       <c r="R2" t="n">
-        <v>6974471.788452435</v>
+        <v>6974440</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80685762</v>
+        <v>80685760</v>
       </c>
       <c r="B3" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545720.2274489661</v>
+        <v>545665</v>
       </c>
       <c r="R3" t="n">
-        <v>6974470.895704246</v>
+        <v>6974484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80685750</v>
+        <v>80685764</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545723.0711735148</v>
+        <v>545719</v>
       </c>
       <c r="R4" t="n">
-        <v>6974430.804114753</v>
+        <v>6974472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80685751</v>
+        <v>80685762</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545729.7925397304</v>
+        <v>545720</v>
       </c>
       <c r="R5" t="n">
-        <v>6974440.0188674</v>
+        <v>6974471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1060,301 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>80685766</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545727</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6974468</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>80685750</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545723</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6974431</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80685765</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>545737</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6974442</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57076-2024 artfynd.xlsx
+++ b/artfynd/A 57076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685751</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685764</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685762</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685750</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,8 +1390,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>